--- a/tame_output/ON/bt/strategyON_20240921.xlsx
+++ b/tame_output/ON/bt/strategyON_20240921.xlsx
@@ -49690,16 +49690,16 @@
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.183883050478626</v>
+        <v>-4.183798645884929</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.259164791693148</v>
+        <v>3.259198553530627</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.466697923031451</v>
+        <v>1.466782327625148</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.813093190017217</v>
+        <v>5.813143832773435</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240921.xlsx
+++ b/tame_output/ON/bt/strategyON_20240921.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.6%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-580.0%</t>
+          <t>-582.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-51.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.2%</t>
+          <t>-321.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-79.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.7%</t>
+          <t>132.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.5%</t>
+          <t>121.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>135.3%</t>
+          <t>134.0%</t>
         </is>
       </c>
     </row>
@@ -49690,16 +49690,16 @@
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.183798645884929</v>
+        <v>-4.20545959137036</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.259198553530627</v>
+        <v>3.250534175336454</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.466782327625148</v>
+        <v>1.445121382139716</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.813143832773435</v>
+        <v>5.800147265482176</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240921.xlsx
+++ b/tame_output/ON/bt/strategyON_20240921.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-70.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-582.1%</t>
+          <t>-573.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-47.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.3%</t>
+          <t>-320.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-76.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.2%</t>
+          <t>132.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.0%</t>
+          <t>121.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>134.0%</t>
+          <t>135.5%</t>
         </is>
       </c>
     </row>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690385612327633</v>
+        <v>-4.629846519690425</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036746812901669</v>
+        <v>2.060962449956553</v>
       </c>
       <c r="F2063" t="n">
         <v>1.246170278916367</v>
@@ -49017,16 +49017,16 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113276</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.73582339215846</v>
+        <v>-4.675284299521252</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.018110064312271</v>
+        <v>2.042325701367155</v>
       </c>
       <c r="F2064" t="n">
         <v>1.203325288238207</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.647616558010882</v>
+        <v>-4.587077465373674</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.073267190821621</v>
+        <v>2.097482827876505</v>
       </c>
       <c r="F2065" t="n">
         <v>1.203325288238207</v>
@@ -49063,16 +49063,16 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.541581562805573</v>
+        <v>-4.481042470168364</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.099381889428473</v>
+        <v>2.123597526483356</v>
       </c>
       <c r="F2066" t="n">
         <v>1.203325288238207</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.358369899672478</v>
+        <v>-4.297830807035269</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.175097504145756</v>
+        <v>2.19931314120064</v>
       </c>
       <c r="F2067" t="n">
         <v>1.203325288238207</v>
@@ -49109,16 +49109,16 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.286648452658627</v>
+        <v>-4.226109360021418</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.169577268799187</v>
+        <v>2.19379290585407</v>
       </c>
       <c r="F2068" t="n">
         <v>1.275046735252058</v>
@@ -49132,16 +49132,16 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.26427542705092</v>
+        <v>-4.203736334413712</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.125442224963441</v>
+        <v>2.149657862018324</v>
       </c>
       <c r="F2069" t="n">
         <v>1.286302486364959</v>
@@ -49155,16 +49155,16 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.297291722961665</v>
+        <v>-4.236752630324457</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.297433911484498</v>
+        <v>2.321649548539381</v>
       </c>
       <c r="F2070" t="n">
         <v>1.216865109698208</v>
@@ -49178,16 +49178,16 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.285764087312057</v>
+        <v>-4.225224994674848</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.29396619157259</v>
+        <v>2.318181828627474</v>
       </c>
       <c r="F2071" t="n">
         <v>1.27586576789957</v>
@@ -49201,16 +49201,16 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.383105588654425</v>
+        <v>-4.322566496017217</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.258697703557432</v>
+        <v>2.282913340612315</v>
       </c>
       <c r="F2072" t="n">
         <v>1.231445585734082</v>
@@ -49224,16 +49224,16 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.468961617994392</v>
+        <v>-4.408422525357183</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.225606374014283</v>
+        <v>2.249822011069166</v>
       </c>
       <c r="F2073" t="n">
         <v>1.189069516507947</v>
@@ -49247,16 +49247,16 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.477798415410511</v>
+        <v>-4.417259322773303</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.204490856868337</v>
+        <v>2.22870649392322</v>
       </c>
       <c r="F2074" t="n">
         <v>1.181627343866596</v>
@@ -49270,16 +49270,16 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.56918097797597</v>
+        <v>-4.508641885338761</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.178102342887203</v>
+        <v>2.202317979942086</v>
       </c>
       <c r="F2075" t="n">
         <v>1.145062459147252</v>
@@ -49293,16 +49293,16 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.557474259988964</v>
+        <v>-4.496935167351755</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.284913287906273</v>
+        <v>2.309128924961156</v>
       </c>
       <c r="F2076" t="n">
         <v>1.156769177134258</v>
@@ -49316,16 +49316,16 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.457810755905301</v>
+        <v>-4.397271663268093</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.327811028271142</v>
+        <v>2.352026665326026</v>
       </c>
       <c r="F2077" t="n">
         <v>1.219956260337945</v>
@@ -49345,10 +49345,10 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.468126854071653</v>
+        <v>-4.407587761434445</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.53658942228266</v>
+        <v>2.560805059337543</v>
       </c>
       <c r="F2078" t="n">
         <v>1.219956260337945</v>
@@ -49362,16 +49362,16 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.468032886054281</v>
+        <v>-4.407493793417072</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.535805676401699</v>
+        <v>2.560021313456582</v>
       </c>
       <c r="F2079" t="n">
         <v>1.220326121685263</v>
@@ -49385,16 +49385,16 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.475251710254125</v>
+        <v>-4.414712617616916</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.527150132666115</v>
+        <v>2.551365769720998</v>
       </c>
       <c r="F2080" t="n">
         <v>1.220326121685263</v>
@@ -49408,16 +49408,16 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.474303287136086</v>
+        <v>-4.413764194498878</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.52752950191333</v>
+        <v>2.551745138968213</v>
       </c>
       <c r="F2081" t="n">
         <v>1.220326121685263</v>
@@ -49437,10 +49437,10 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.631371745391711</v>
+        <v>-4.570832652754502</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.477429726592173</v>
+        <v>2.501645363647056</v>
       </c>
       <c r="F2082" t="n">
         <v>1.220326121685263</v>
@@ -49460,10 +49460,10 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.625379498602899</v>
+        <v>-4.564840405965691</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.481772623732085</v>
+        <v>2.505988260786968</v>
       </c>
       <c r="F2083" t="n">
         <v>1.220326121685263</v>
@@ -49483,10 +49483,10 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.536821537472131</v>
+        <v>-4.476282444834923</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.510849944202161</v>
+        <v>2.535065581257044</v>
       </c>
       <c r="F2084" t="n">
         <v>1.220326121685263</v>
@@ -49506,10 +49506,10 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.519062459969057</v>
+        <v>-4.458523367331849</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.517262252642386</v>
+        <v>2.541477889697269</v>
       </c>
       <c r="F2085" t="n">
         <v>1.220326121685263</v>
@@ -49529,10 +49529,10 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.41943230891999</v>
+        <v>-4.358893216282781</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.5698964989706</v>
+        <v>2.594112136025483</v>
       </c>
       <c r="F2086" t="n">
         <v>1.31995627273433</v>
@@ -49552,10 +49552,10 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.468831817609001</v>
+        <v>-4.408292724971792</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.739290960993722</v>
+        <v>2.763506598048605</v>
       </c>
       <c r="F2087" t="n">
         <v>1.330215106166075</v>
@@ -49575,10 +49575,10 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.262147343966625</v>
+        <v>-4.201608251329416</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.809153423553535</v>
+        <v>2.833369060608418</v>
       </c>
       <c r="F2088" t="n">
         <v>1.536899579808451</v>
@@ -49598,10 +49598,10 @@
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.296304238964151</v>
+        <v>-4.235765146326942</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.797492179208629</v>
+        <v>2.821707816263512</v>
       </c>
       <c r="F2089" t="n">
         <v>1.453315810267638</v>
@@ -49621,10 +49621,10 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.203714759902694</v>
+        <v>-4.143175667265486</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.188025084822879</v>
+        <v>3.212240721877762</v>
       </c>
       <c r="F2090" t="n">
         <v>1.453315810267638</v>
@@ -49644,10 +49644,10 @@
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.263603387726245</v>
+        <v>-4.203064295089036</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.168632745260562</v>
+        <v>3.192848382315446</v>
       </c>
       <c r="F2091" t="n">
         <v>1.439193895580174</v>
@@ -49667,10 +49667,10 @@
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.211387077929903</v>
+        <v>-4.150847985292694</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.239349210502626</v>
+        <v>3.26356484755751</v>
       </c>
       <c r="F2092" t="n">
         <v>1.439193895580174</v>
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.761023110786022</v>
+        <v>3.873573440512898</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.20545959137036</v>
+        <v>-4.118950468207449</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.250534175336454</v>
+        <v>3.285137824601619</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.445121382139716</v>
+        <v>1.471091412665419</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.800147265482176</v>
+        <v>5.815729283797598</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240921.xlsx
+++ b/tame_output/ON/bt/strategyON_20240921.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>115.1%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>181.7%</t>
+          <t>176.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.2%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.2%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.2%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-573.5%</t>
+          <t>-584.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-52.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>113.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.4%</t>
+          <t>-321.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-78.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.8%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,21 +1433,21 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2023-12-28</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.1%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>41.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2093"/>
+  <dimension ref="A1:G2094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.946839784467805</v>
+        <v>-3.993508139155452</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.96219569739148</v>
+        <v>1.943528355516421</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.146241957519543</v>
+        <v>1.131360351746248</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.229033210004077</v>
+        <v>4.2201042465401</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.891509196566043</v>
+        <v>-3.93817755125369</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.019294869164243</v>
+        <v>2.000627527289184</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.201572545421305</v>
+        <v>1.18669093964801</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.297198499357192</v>
+        <v>4.288269535893215</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.87945506965308</v>
+        <v>-3.926123424340727</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.017803087830866</v>
+        <v>1.999135745955807</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.213626672334268</v>
+        <v>1.198745066560973</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.298117543406407</v>
+        <v>4.28918857994243</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.920610189221301</v>
+        <v>-3.967278543908948</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.003221670187714</v>
+        <v>1.984554328312655</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.172471552766047</v>
+        <v>1.157589946992752</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.275305101849611</v>
+        <v>4.266376138385634</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.852561626529771</v>
+        <v>-3.899229981217418</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.043292121142208</v>
+        <v>2.02462477926715</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>1.225638509684282</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.320056301878434</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.084162019699273</v>
+        <v>-4.130830374386919</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.970854634048002</v>
+        <v>1.952187292172943</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>1.225638509684282</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.340258972052029</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134213565228492</v>
+        <v>-4.180881919916139</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934440251903196</v>
+        <v>1.915772910028137</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>1.225638509684282</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.32386520811891</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309320397804937</v>
+        <v>-4.355988752492584</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824649432466085</v>
+        <v>1.805982090591026</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>1.225638509684282</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.284117121712377</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113220244374414</v>
+        <v>-4.159888599062061</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910112112835234</v>
+        <v>1.891444770960175</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.421738663114805</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.408799832767631</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96019485226113</v>
+        <v>-4.006863206948777</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070493269253452</v>
+        <v>2.051825927378393</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.574764055228089</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.599786067608505</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.9885021661344</v>
+        <v>-4.035170520822048</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246636568612437</v>
+        <v>2.227969226737378</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.574764055228089</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.787252292516798</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155095391247922</v>
+        <v>-4.20176374593557</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14940222992111</v>
+        <v>2.130734888046052</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.408170830114566</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.656699308802767</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132059597886356</v>
+        <v>-4.178727952574004</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.162292949927454</v>
+        <v>2.143625608052396</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.408170830114566</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.660375711464485</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399468</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.10281361743066</v>
+        <v>-4.149481972118307</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171609397233228</v>
+        <v>2.15294205535817</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.408170830114566</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.65799376658798</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256369</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.209739165308511</v>
+        <v>-4.256407519996158</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.126132417239723</v>
+        <v>2.107465075364664</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>1.301245282236715</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.591131677018905</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.35475772381576</v>
+        <v>-4.401426078503407</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069553795980058</v>
+        <v>2.050886454104999</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>1.156226723729467</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.50554934405779</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687011</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473099489600477</v>
+        <v>-4.519767844288125</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.122148328923924</v>
+        <v>2.103480987048865</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>1.166912762292357</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.611892206453277</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790801</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524509911921185</v>
+        <v>-4.571178266608833</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099369857121579</v>
+        <v>2.080702515246521</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>1.166912762292357</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.609677903579215</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603929363128937</v>
+        <v>-4.650597717816584</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067505204712768</v>
+        <v>2.04883786283771</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>1.166912762292357</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.609581031653505</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298395</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699392361046154</v>
+        <v>-4.746060715733802</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.029313899103924</v>
+        <v>2.010646557228865</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>1.166912762292357</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.609574925211548</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635016450195439</v>
+        <v>-4.681684804883087</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053160660006821</v>
+        <v>2.034493318131762</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>1.231288673143072</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.646296868284588</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.629846519690425</v>
+        <v>-4.737053967015281</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.060962449956553</v>
+        <v>2.018079471026611</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>1.231288673143072</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.652030686032314</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.675284299521252</v>
+        <v>-4.782491746846108</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.042325701367155</v>
+        <v>1.999442722437212</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.203325288238207</v>
+        <v>1.188443682464912</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.634791018432328</v>
+        <v>4.625862054968351</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.587077465373674</v>
+        <v>-4.69428491269853</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.097482827876505</v>
+        <v>2.054599848946562</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.203325288238207</v>
+        <v>1.188443682464912</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.654665411282647</v>
+        <v>4.64573644781867</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.481042470168364</v>
+        <v>-4.58824991749322</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.123597526483356</v>
+        <v>2.080714547553414</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.203325288238207</v>
+        <v>1.188443682464912</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.638366111807374</v>
+        <v>4.629437148343397</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.297830807035269</v>
+        <v>-4.405038254360125</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.19931314120064</v>
+        <v>2.156430162270698</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.203325288238207</v>
+        <v>1.188443682464912</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.64079706127142</v>
+        <v>4.631868097807443</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.226109360021418</v>
+        <v>-4.333316807346274</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.19379290585407</v>
+        <v>2.150909926924128</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.275046735252058</v>
+        <v>1.260165129478763</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.64962111532762</v>
+        <v>4.640692151863643</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.203736334413712</v>
+        <v>-4.310943781738568</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.149657862018324</v>
+        <v>2.106774883088382</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.286302486364959</v>
+        <v>1.271420880591664</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.603290311916533</v>
+        <v>4.594361348452556</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.236752630324457</v>
+        <v>-4.343960077649313</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.321649548539381</v>
+        <v>2.278766569609439</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.216865109698208</v>
+        <v>1.201983503924913</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.746826090801837</v>
+        <v>4.73789712733786</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.225224994674848</v>
+        <v>-4.332432441999704</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.318181828627474</v>
+        <v>2.275298849697532</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.27586576789957</v>
+        <v>1.260984162126275</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.774147711550904</v>
+        <v>4.765218748086927</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.322566496017217</v>
+        <v>-4.429773943342073</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.282913340612315</v>
+        <v>2.240030361682373</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.231445585734082</v>
+        <v>1.216563979960787</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.751163714773399</v>
+        <v>4.742234751309422</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.408422525357183</v>
+        <v>-4.515629972682039</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.249822011069166</v>
+        <v>2.206939032139224</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.189069516507947</v>
+        <v>1.174187910734652</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.726989155430556</v>
+        <v>4.718060191966579</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.417259322773303</v>
+        <v>-4.524466770098159</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.22870649392322</v>
+        <v>2.185823514993278</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.181627343866596</v>
+        <v>1.166745738093301</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.704943053666248</v>
+        <v>4.69601409020227</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.508641885338761</v>
+        <v>-4.615849332663617</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.202317979942086</v>
+        <v>2.159435001012144</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.145062459147252</v>
+        <v>1.130180853373957</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.69316863387969</v>
+        <v>4.684239670415713</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.496935167351755</v>
+        <v>-4.604142614676611</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.309128924961156</v>
+        <v>2.266245946031214</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.156769177134258</v>
+        <v>1.141887571360963</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.802320922496161</v>
+        <v>4.793391959032184</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.397271663268093</v>
+        <v>-4.504479110592949</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.352026665326026</v>
+        <v>2.309143686396084</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.219956260337945</v>
+        <v>1.20507465456465</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.843265511149778</v>
+        <v>4.834336547685801</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.407587761434445</v>
+        <v>-4.514795208759301</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.560805059337543</v>
+        <v>2.517922080407601</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.219956260337945</v>
+        <v>1.20507465456465</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.056170344427836</v>
+        <v>5.047241380963859</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.407493793417072</v>
+        <v>-4.514701240741928</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.560021313456582</v>
+        <v>2.51713833452664</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.220326121685263</v>
+        <v>1.205444515911968</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.055570928148317</v>
+        <v>5.04664196468434</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.414712617616916</v>
+        <v>-4.521920064941773</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.551365769720998</v>
+        <v>2.508482790791056</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.220326121685263</v>
+        <v>1.205444515911968</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.049802914092671</v>
+        <v>5.040873950628693</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.413764194498878</v>
+        <v>-4.520971641823734</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.551745138968213</v>
+        <v>2.508862160038271</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.220326121685263</v>
+        <v>1.205444515911968</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.049802914092671</v>
+        <v>5.040873950628693</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.570832652754502</v>
+        <v>-4.678040100079358</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.501645363647056</v>
+        <v>2.458762384717114</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.220326121685263</v>
+        <v>1.205444515911968</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.062530522073763</v>
+        <v>5.053601558609786</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.564840405965691</v>
+        <v>-4.672047853290547</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.505988260786968</v>
+        <v>2.463105281857026</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.220326121685263</v>
+        <v>1.205444515911968</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.06447652049815</v>
+        <v>5.055547557034173</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.476282444834923</v>
+        <v>-4.583489892159779</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.535065581257044</v>
+        <v>2.492182602327102</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.220326121685263</v>
+        <v>1.205444515911968</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.058130656515919</v>
+        <v>5.049201693051942</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.458523367331849</v>
+        <v>-4.565730814656705</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.541477889697269</v>
+        <v>2.498594910767327</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.220326121685263</v>
+        <v>1.205444515911968</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.057439333954915</v>
+        <v>5.048510370490938</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.358893216282781</v>
+        <v>-4.466100663607637</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.594112136025483</v>
+        <v>2.551229157095541</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.31995627273433</v>
+        <v>1.305074666961035</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.129999610492942</v>
+        <v>5.121070647028965</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.408292724971792</v>
+        <v>-4.515500172296648</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.763506598048605</v>
+        <v>2.720623619118663</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.330215106166075</v>
+        <v>1.31533350039278</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.325309176050715</v>
+        <v>5.316380212586738</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.201608251329416</v>
+        <v>-4.308815698654272</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.833369060608418</v>
+        <v>2.790486081678476</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.536899579808451</v>
+        <v>1.522017974035156</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.436508533339003</v>
+        <v>5.427579569875026</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.235765146326942</v>
+        <v>-4.342972593651798</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.821707816263512</v>
+        <v>2.77882483733357</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.453315810267638</v>
+        <v>1.438434204494343</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.38835978526862</v>
+        <v>5.379430821804643</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.143175667265486</v>
+        <v>-4.250383114590342</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.212240721877762</v>
+        <v>3.16935774294782</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.453315810267638</v>
+        <v>1.438434204494343</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.741856899258288</v>
+        <v>5.732927935794311</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.203064295089036</v>
+        <v>-4.310271742413892</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.192848382315446</v>
+        <v>3.149965403385504</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.439193895580174</v>
+        <v>1.424312289806879</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.737946862012913</v>
+        <v>5.729017898548936</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.150847985292694</v>
+        <v>-4.25805543261755</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.26356484755751</v>
+        <v>3.220681868627568</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.439193895580174</v>
+        <v>1.424312289806879</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.78777680333644</v>
+        <v>5.778847839872463</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,45 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.873573440512898</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.118950468207449</v>
+        <v>-4.226157915532305</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.285137824601619</v>
+        <v>3.242254845671677</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.471091412665419</v>
+        <v>1.456209806892124</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.815729283797598</v>
+        <v>5.806800320333621</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="2" t="n">
+        <v>45556</v>
+      </c>
+      <c r="B2094" t="n">
+        <v>3.761950932259855</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>4.885641196543398</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>-4.226157915532305</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>3.242254845671677</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>1.456209806892124</v>
+      </c>
+      <c r="G2094" t="n">
+        <v>4.878704993529766</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240921.xlsx
+++ b/tame_output/ON/bt/strategyON_20240921.xlsx
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399468</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256369</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687011</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790801</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298395</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>

--- a/tame_output/ON/bt/strategyON_20240921.xlsx
+++ b/tame_output/ON/bt/strategyON_20240921.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>118.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>176.9%</t>
+          <t>191.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>422.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-584.2%</t>
+          <t>-576.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-44.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>113.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-321.1%</t>
+          <t>-320.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-75.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,21 +1433,21 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2023-12-28</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.993508139155452</v>
+        <v>-3.946839784467805</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.943528355516421</v>
+        <v>1.96219569739148</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.131360351746248</v>
+        <v>1.146241957519543</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.2201042465401</v>
+        <v>4.229033210004077</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.93817755125369</v>
+        <v>-3.891509196566043</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.000627527289184</v>
+        <v>2.019294869164243</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.18669093964801</v>
+        <v>1.201572545421305</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.288269535893215</v>
+        <v>4.297198499357192</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.926123424340727</v>
+        <v>-3.87945506965308</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.999135745955807</v>
+        <v>2.017803087830866</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.198745066560973</v>
+        <v>1.213626672334268</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.28918857994243</v>
+        <v>4.298117543406407</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.967278543908948</v>
+        <v>-3.920610189221301</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.984554328312655</v>
+        <v>2.003221670187714</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.157589946992752</v>
+        <v>1.172471552766047</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.266376138385634</v>
+        <v>4.275305101849611</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.899229981217418</v>
+        <v>-3.852561626529771</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.02462477926715</v>
+        <v>2.043292121142208</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.225638509684282</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.320056301878434</v>
+        <v>4.328985265342411</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.130830374386919</v>
+        <v>-4.084162019699273</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.952187292172943</v>
+        <v>1.970854634048002</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.225638509684282</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.340258972052029</v>
+        <v>4.349187935516005</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.180881919916139</v>
+        <v>-4.134213565228492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.915772910028137</v>
+        <v>1.934440251903196</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.225638509684282</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.32386520811891</v>
+        <v>4.332794171582887</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.355988752492584</v>
+        <v>-4.309320397804937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.805982090591026</v>
+        <v>1.824649432466085</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.225638509684282</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.284117121712377</v>
+        <v>4.293046085176353</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.159888599062061</v>
+        <v>-4.113220244374414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.891444770960175</v>
+        <v>1.910112112835234</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.421738663114805</v>
+        <v>1.4366202688881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.408799832767631</v>
+        <v>4.417728796231607</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.006863206948777</v>
+        <v>-3.96019485226113</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.051825927378393</v>
+        <v>2.070493269253452</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.574764055228089</v>
+        <v>1.589645661001384</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.599786067608505</v>
+        <v>4.608715031072482</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.035170520822048</v>
+        <v>-3.9885021661344</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.227969226737378</v>
+        <v>2.246636568612437</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.574764055228089</v>
+        <v>1.589645661001384</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.787252292516798</v>
+        <v>4.796181255980775</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.20176374593557</v>
+        <v>-4.155095391247922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.130734888046052</v>
+        <v>2.14940222992111</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.408170830114566</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.656699308802767</v>
+        <v>4.665628272266744</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.178727952574004</v>
+        <v>-4.132059597886356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.143625608052396</v>
+        <v>2.162292949927454</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.408170830114566</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.660375711464485</v>
+        <v>4.669304674928462</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.149481972118307</v>
+        <v>-4.10281361743066</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.15294205535817</v>
+        <v>2.171609397233228</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.408170830114566</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.65799376658798</v>
+        <v>4.666922730051957</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.256407519996158</v>
+        <v>-4.209739165308511</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.107465075364664</v>
+        <v>2.126132417239723</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.301245282236715</v>
+        <v>1.31612688801001</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.591131677018905</v>
+        <v>4.600060640482882</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.401426078503407</v>
+        <v>-4.35475772381576</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.050886454104999</v>
+        <v>2.069553795980058</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.156226723729467</v>
+        <v>1.171108329502762</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.50554934405779</v>
+        <v>4.514478307521767</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.519767844288125</v>
+        <v>-4.473099489600477</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.103480987048865</v>
+        <v>2.122148328923924</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.166912762292357</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.611892206453277</v>
+        <v>4.620821169917254</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.571178266608833</v>
+        <v>-4.524509911921185</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.080702515246521</v>
+        <v>2.099369857121579</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.166912762292357</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.609677903579215</v>
+        <v>4.618606867043193</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.650597717816584</v>
+        <v>-4.603929363128937</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.04883786283771</v>
+        <v>2.067505204712768</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.166912762292357</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.609581031653505</v>
+        <v>4.618509995117482</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.746060715733802</v>
+        <v>-4.699392361046154</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.010646557228865</v>
+        <v>2.029313899103924</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.166912762292357</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.609574925211548</v>
+        <v>4.618503888675525</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.681684804883087</v>
+        <v>-4.635016450195439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.034493318131762</v>
+        <v>2.053160660006821</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.231288673143072</v>
+        <v>1.246170278916367</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.646296868284588</v>
+        <v>4.655225831748565</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.737053967015281</v>
+        <v>-4.690385612327633</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.018079471026611</v>
+        <v>2.036746812901669</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.231288673143072</v>
+        <v>1.246170278916367</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.652030686032314</v>
+        <v>4.660959649496291</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113276</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.782491746846108</v>
+        <v>-4.73582339215846</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.999442722437212</v>
+        <v>2.018110064312271</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.188443682464912</v>
+        <v>1.203325288238207</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.625862054968351</v>
+        <v>4.634791018432328</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.69428491269853</v>
+        <v>-4.647616558010882</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.054599848946562</v>
+        <v>2.073267190821621</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.188443682464912</v>
+        <v>1.203325288238207</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.64573644781867</v>
+        <v>4.654665411282647</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.58824991749322</v>
+        <v>-4.541581562805573</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.080714547553414</v>
+        <v>2.099381889428473</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.188443682464912</v>
+        <v>1.203325288238207</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.629437148343397</v>
+        <v>4.638366111807374</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.405038254360125</v>
+        <v>-4.358369899672478</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.156430162270698</v>
+        <v>2.175097504145756</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.188443682464912</v>
+        <v>1.203325288238207</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.631868097807443</v>
+        <v>4.64079706127142</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.333316807346274</v>
+        <v>-4.286648452658627</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.150909926924128</v>
+        <v>2.169577268799187</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.260165129478763</v>
+        <v>1.275046735252058</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.640692151863643</v>
+        <v>4.64962111532762</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.310943781738568</v>
+        <v>-4.26427542705092</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.106774883088382</v>
+        <v>2.125442224963441</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.271420880591664</v>
+        <v>1.286302486364959</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.594361348452556</v>
+        <v>4.603290311916533</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.343960077649313</v>
+        <v>-4.297291722961665</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.278766569609439</v>
+        <v>2.297433911484498</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.201983503924913</v>
+        <v>1.216865109698208</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.73789712733786</v>
+        <v>4.746826090801837</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.332432441999704</v>
+        <v>-4.285764087312057</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.275298849697532</v>
+        <v>2.29396619157259</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.260984162126275</v>
+        <v>1.27586576789957</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.765218748086927</v>
+        <v>4.774147711550904</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.429773943342073</v>
+        <v>-4.383105588654425</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.240030361682373</v>
+        <v>2.258697703557432</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.216563979960787</v>
+        <v>1.231445585734082</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.742234751309422</v>
+        <v>4.751163714773399</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942768</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.013547445525788</v>
+        <v>4.053808421694392</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.515629972682039</v>
+        <v>-4.437219460358931</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.206939032139224</v>
+        <v>2.278564213237072</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.174187910734652</v>
+        <v>1.201341381561784</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.718060191966579</v>
+        <v>4.774613250631463</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>4.036227623514894</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.524466770098159</v>
+        <v>-4.446056257775051</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.185823514993278</v>
+        <v>2.257448696091126</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.166745738093301</v>
+        <v>1.193899208920433</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.69601409020227</v>
+        <v>4.752567148867154</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>4.046392134559944</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.615849332663617</v>
+        <v>-4.537438820340509</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.159435001012144</v>
+        <v>2.231060182109992</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.130180853373957</v>
+        <v>1.157334324201089</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.684239670415713</v>
+        <v>4.740792729080597</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889187</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.148520392384212</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.604142614676611</v>
+        <v>-4.525732102353503</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.266245946031214</v>
+        <v>2.337871127129063</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.141887571360963</v>
+        <v>1.169041042188095</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.793391959032184</v>
+        <v>4.849945017697069</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.151552731115617</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.504479110592949</v>
+        <v>-4.426068598269841</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.309143686396084</v>
+        <v>2.380768867493932</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.20507465456465</v>
+        <v>1.232228125391781</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.834336547685801</v>
+        <v>4.890889606350686</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.364457564393675</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.514795208759301</v>
+        <v>-4.436384696436193</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.517922080407601</v>
+        <v>2.58954726150545</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.20507465456465</v>
+        <v>1.232228125391781</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.047241380963859</v>
+        <v>5.103794439628744</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.363636231305764</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.514701240741928</v>
+        <v>-4.43629072841882</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.51713833452664</v>
+        <v>2.588763515624488</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.205444515911968</v>
+        <v>1.232597986739099</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.04664196468434</v>
+        <v>5.103195023349224</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.357868217250118</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.521920064941773</v>
+        <v>-4.443509552618664</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.508482790791056</v>
+        <v>2.580107971888904</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.205444515911968</v>
+        <v>1.232597986739099</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.040873950628693</v>
+        <v>5.097427009293578</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.357868217250118</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.520971641823734</v>
+        <v>-4.442561129500626</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.508862160038271</v>
+        <v>2.58048734113612</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.205444515911968</v>
+        <v>1.232597986739099</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.040873950628693</v>
+        <v>5.097427009293578</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.37059582523121</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.678040100079358</v>
+        <v>-4.599629587756249</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.458762384717114</v>
+        <v>2.530387565814963</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.205444515911968</v>
+        <v>1.232597986739099</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.053601558609786</v>
+        <v>5.11015461727467</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.372541823655598</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.672047853290547</v>
+        <v>-4.593637340967438</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.463105281857026</v>
+        <v>2.534730462954875</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.205444515911968</v>
+        <v>1.232597986739099</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.055547557034173</v>
+        <v>5.112100615699058</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.366195959673367</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.583489892159779</v>
+        <v>-4.50507937983667</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.492182602327102</v>
+        <v>2.563807783424951</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.205444515911968</v>
+        <v>1.232597986739099</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.049201693051942</v>
+        <v>5.105754751716827</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.365504637112362</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.565730814656705</v>
+        <v>-4.487320302333596</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.498594910767327</v>
+        <v>2.570220091865176</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.205444515911968</v>
+        <v>1.232597986739099</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.048510370490938</v>
+        <v>5.105063429155822</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.378286823020949</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.466100663607637</v>
+        <v>-4.387690151284528</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.551229157095541</v>
+        <v>2.62285433819339</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.305074666961035</v>
+        <v>1.332228137788167</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.121070647028965</v>
+        <v>5.17762370569385</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.567441088519676</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.515500172296648</v>
+        <v>-4.437089659973539</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.720623619118663</v>
+        <v>2.792248800216512</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.31533350039278</v>
+        <v>1.342486971219912</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.316380212586738</v>
+        <v>5.372933271251623</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.554629761622538</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.308815698654272</v>
+        <v>-4.230405186331163</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.790486081678476</v>
+        <v>2.862111262776325</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.522017974035156</v>
+        <v>1.549171444862287</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.427579569875026</v>
+        <v>5.484132628539911</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.516370299108037</v>
+        <v>4.556631275276643</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.342972593651798</v>
+        <v>-4.264562081328689</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.77882483733357</v>
+        <v>2.850450018431419</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.438434204494343</v>
+        <v>1.465587675321475</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.379430821804643</v>
+        <v>5.435983880469528</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.869867413097705</v>
+        <v>4.91012838926631</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.250383114590342</v>
+        <v>-4.171972602267233</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.16935774294782</v>
+        <v>3.240982924045669</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.438434204494343</v>
+        <v>1.465587675321475</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.732927935794311</v>
+        <v>5.789480994459195</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.874430524664808</v>
+        <v>4.914691500833413</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.310271742413892</v>
+        <v>-4.231861230090783</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.149965403385504</v>
+        <v>3.221590584483352</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.424312289806879</v>
+        <v>1.45146576063401</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.729017898548936</v>
+        <v>5.78557095721382</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.83520244110356</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.924260465988335</v>
+        <v>4.964521442156941</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.25805543261755</v>
+        <v>-4.179644920294441</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.220681868627568</v>
+        <v>3.292307049725416</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.424312289806879</v>
+        <v>1.45146576063401</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.778847839872463</v>
+        <v>5.835400898537348</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.933074436198346</v>
+        <v>4.973335412366952</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.226157915532305</v>
+        <v>-4.147747403209196</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.242254845671677</v>
+        <v>3.313880026769525</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.456209806892124</v>
+        <v>1.483363277719256</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.806800320333621</v>
+        <v>5.863353378998506</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.761950932259855</v>
+        <v>3.849469723131095</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.885641196543398</v>
+        <v>5.027002313160696</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.226157915532305</v>
+        <v>-4.147747403209196</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.242254845671677</v>
+        <v>3.313880026769525</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.456209806892124</v>
+        <v>1.483363277719256</v>
       </c>
       <c r="G2094" t="n">
-        <v>4.878704993529766</v>
+        <v>5.020066110147064</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240921.xlsx
+++ b/tame_output/ON/bt/strategyON_20240921.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>191.1%</t>
+          <t>181.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-36.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-576.3%</t>
+          <t>-578.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-44.8%</t>
+          <t>-50.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.5%</t>
+          <t>113.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.6%</t>
+          <t>-320.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-77.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>132.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>121.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>134.9%</t>
         </is>
       </c>
     </row>
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.891509196566043</v>
+        <v>-3.89483403629534</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.019294869164243</v>
+        <v>2.017964933272524</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.201572545421305</v>
+        <v>1.198247705692008</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.297198499357192</v>
+        <v>4.295203595519613</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.87945506965308</v>
+        <v>-3.882779909382378</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.017803087830866</v>
+        <v>2.016473151939147</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.213626672334268</v>
+        <v>1.210301832604971</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.298117543406407</v>
+        <v>4.296122639568829</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.920610189221301</v>
+        <v>-3.923935028950599</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.003221670187714</v>
+        <v>2.001891734295995</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.172471552766047</v>
+        <v>1.16914671303675</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.275305101849611</v>
+        <v>4.273310198012032</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.852561626529771</v>
+        <v>-3.855886466259069</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.043292121142208</v>
+        <v>2.041962185250489</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>1.23719527572828</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.326990361504833</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.084162019699273</v>
+        <v>-4.087486859428569</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.970854634048002</v>
+        <v>1.969524698156283</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>1.23719527572828</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.347193031678427</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134213565228492</v>
+        <v>-4.137538404957789</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934440251903196</v>
+        <v>1.933110316011477</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>1.23719527572828</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.330799267745309</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309320397804937</v>
+        <v>-4.312645237534234</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824649432466085</v>
+        <v>1.823319496574366</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>1.23719527572828</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.291051181338775</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113220244374414</v>
+        <v>-4.116545084103711</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910112112835234</v>
+        <v>1.908782176943515</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.433295429158802</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.415733892394029</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96019485226113</v>
+        <v>-3.963519691990427</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070493269253452</v>
+        <v>2.069163333361733</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.586320821272087</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.606720127234905</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.9885021661344</v>
+        <v>-3.991827005863697</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246636568612437</v>
+        <v>2.245306632720718</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.586320821272087</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.794186352143196</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155095391247922</v>
+        <v>-4.158420230977219</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14940222992111</v>
+        <v>2.148072294029391</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.419727596158564</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.663633368429166</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132059597886356</v>
+        <v>-4.135384437615653</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.162292949927454</v>
+        <v>2.160963014035736</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.419727596158564</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.667309771090884</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.10281361743066</v>
+        <v>-4.106138457159957</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171609397233228</v>
+        <v>2.17027946134151</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.419727596158564</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.664927826214379</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.209739165308511</v>
+        <v>-4.213064005037808</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.126132417239723</v>
+        <v>2.124802481348004</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>1.312802048280713</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.598065736645303</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.35475772381576</v>
+        <v>-4.358082563545056</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069553795980058</v>
+        <v>2.068223860088339</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>1.167783489773464</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.512483403684188</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473099489600477</v>
+        <v>-4.476424329329774</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.122148328923924</v>
+        <v>2.120818393032205</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>1.178469528336354</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.618826266079675</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524509911921185</v>
+        <v>-4.527834751650482</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099369857121579</v>
+        <v>2.098039921229861</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>1.178469528336354</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.616611963205615</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603929363128937</v>
+        <v>-4.607254202858234</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067505204712768</v>
+        <v>2.066175268821049</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>1.178469528336354</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.616515091279903</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699392361046154</v>
+        <v>-4.702717200775451</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.029313899103924</v>
+        <v>2.027983963212205</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>1.178469528336354</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.616508984837947</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635016450195439</v>
+        <v>-4.638341289924736</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053160660006821</v>
+        <v>2.051830724115102</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>1.24284543918707</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.653230927910986</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690385612327633</v>
+        <v>-4.69371045205693</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036746812901669</v>
+        <v>2.035416877009951</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>1.24284543918707</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.658964745658713</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.73582339215846</v>
+        <v>-4.739148231887757</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.018110064312271</v>
+        <v>2.016780128420553</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.203325288238207</v>
+        <v>1.20000044850891</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.634791018432328</v>
+        <v>4.63279611459475</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.647616558010882</v>
+        <v>-4.650941397740179</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.073267190821621</v>
+        <v>2.071937254929902</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.203325288238207</v>
+        <v>1.20000044850891</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.654665411282647</v>
+        <v>4.652670507445068</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.541581562805573</v>
+        <v>-4.54490640253487</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.099381889428473</v>
+        <v>2.098051953536754</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.203325288238207</v>
+        <v>1.20000044850891</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.638366111807374</v>
+        <v>4.636371207969797</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.358369899672478</v>
+        <v>-4.361694739401774</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.175097504145756</v>
+        <v>2.173767568254037</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.203325288238207</v>
+        <v>1.20000044850891</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.64079706127142</v>
+        <v>4.638802157433842</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.286648452658627</v>
+        <v>-4.289973292387923</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.169577268799187</v>
+        <v>2.168247332907468</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.275046735252058</v>
+        <v>1.271721895522761</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.64962111532762</v>
+        <v>4.647626211490042</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.26427542705092</v>
+        <v>-4.267600266780217</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.125442224963441</v>
+        <v>2.124112289071722</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.286302486364959</v>
+        <v>1.282977646635662</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.603290311916533</v>
+        <v>4.601295408078954</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.297291722961665</v>
+        <v>-4.300616562690962</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.297433911484498</v>
+        <v>2.296103975592779</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.216865109698208</v>
+        <v>1.213540269968911</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.746826090801837</v>
+        <v>4.744831186964259</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.285764087312057</v>
+        <v>-4.289088927041353</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.29396619157259</v>
+        <v>2.292636255680872</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.27586576789957</v>
+        <v>1.272540928170273</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.774147711550904</v>
+        <v>4.772152807713325</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.383105588654425</v>
+        <v>-4.386430428383722</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.258697703557432</v>
+        <v>2.257367767665713</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.231445585734082</v>
+        <v>1.228120746004785</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.751163714773399</v>
+        <v>4.749168810935821</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.053808421694392</v>
+        <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.437219460358931</v>
+        <v>-4.472286457723689</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.278564213237072</v>
+        <v>2.224276438122565</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.201341381561784</v>
+        <v>1.18574467677865</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.774613250631463</v>
+        <v>4.724994251592978</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.036227623514894</v>
+        <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.446056257775051</v>
+        <v>-4.481123255139808</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.257448696091126</v>
+        <v>2.203160920976618</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.193899208920433</v>
+        <v>1.178302504137299</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.752567148867154</v>
+        <v>4.70294814982867</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.046392134559944</v>
+        <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.537438820340509</v>
+        <v>-4.572505817705267</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.231060182109992</v>
+        <v>2.176772406995484</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.157334324201089</v>
+        <v>1.141737619417954</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.740792729080597</v>
+        <v>4.691173730042112</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.148520392384212</v>
+        <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.525732102353503</v>
+        <v>-4.560799099718261</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.337871127129063</v>
+        <v>2.283583352014554</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.169041042188095</v>
+        <v>1.153444337404961</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.849945017697069</v>
+        <v>4.800326018658583</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.151552731115617</v>
+        <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.426068598269841</v>
+        <v>-4.461135595634598</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.380768867493932</v>
+        <v>2.326481092379424</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.232228125391781</v>
+        <v>1.216631420608647</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.890889606350686</v>
+        <v>4.841270607312199</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.364457564393675</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.436384696436193</v>
+        <v>-4.47145169380095</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.58954726150545</v>
+        <v>2.535259486390941</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.232228125391781</v>
+        <v>1.216631420608647</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.103794439628744</v>
+        <v>5.054175440590257</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.363636231305764</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.43629072841882</v>
+        <v>-4.471357725783577</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.588763515624488</v>
+        <v>2.53447574050998</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.232597986739099</v>
+        <v>1.217001281955965</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.103195023349224</v>
+        <v>5.053576024310738</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.357868217250118</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.443509552618664</v>
+        <v>-4.478576549983422</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.580107971888904</v>
+        <v>2.525820196774396</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.232597986739099</v>
+        <v>1.217001281955965</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.097427009293578</v>
+        <v>5.047808010255092</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.357868217250118</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.442561129500626</v>
+        <v>-4.477628126865383</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.58048734113612</v>
+        <v>2.526199566021611</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.232597986739099</v>
+        <v>1.217001281955965</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.097427009293578</v>
+        <v>5.047808010255092</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.37059582523121</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.599629587756249</v>
+        <v>-4.634696585121008</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.530387565814963</v>
+        <v>2.476099790700454</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.232597986739099</v>
+        <v>1.217001281955965</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.11015461727467</v>
+        <v>5.060535618236184</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.372541823655598</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.593637340967438</v>
+        <v>-4.628704338332196</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.534730462954875</v>
+        <v>2.480442687840366</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.232597986739099</v>
+        <v>1.217001281955965</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.112100615699058</v>
+        <v>5.062481616660572</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.366195959673367</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.50507937983667</v>
+        <v>-4.540146377201428</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.563807783424951</v>
+        <v>2.509520008310442</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.232597986739099</v>
+        <v>1.217001281955965</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.105754751716827</v>
+        <v>5.05613575267834</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.365504637112362</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.487320302333596</v>
+        <v>-4.522387299698354</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.570220091865176</v>
+        <v>2.515932316750667</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.232597986739099</v>
+        <v>1.217001281955965</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.105063429155822</v>
+        <v>5.055444430117336</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.378286823020949</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.387690151284528</v>
+        <v>-4.422757148649286</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.62285433819339</v>
+        <v>2.568566563078881</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.332228137788167</v>
+        <v>1.316631433005033</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.17762370569385</v>
+        <v>5.128004706655364</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.567441088519676</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.437089659973539</v>
+        <v>-4.472156657338298</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.792248800216512</v>
+        <v>2.737961025102003</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.342486971219912</v>
+        <v>1.326890266436778</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.372933271251623</v>
+        <v>5.323314272213137</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.554629761622538</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.230405186331163</v>
+        <v>-4.265472183695922</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.862111262776325</v>
+        <v>2.807823487661816</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.549171444862287</v>
+        <v>1.533574740079153</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.484132628539911</v>
+        <v>5.434513629501424</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.556631275276643</v>
+        <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.264562081328689</v>
+        <v>-4.299629078693448</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.850450018431419</v>
+        <v>2.79616224331691</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.465587675321475</v>
+        <v>1.449990970538341</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.435983880469528</v>
+        <v>5.386364881431042</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.91012838926631</v>
+        <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.171972602267233</v>
+        <v>-4.207039599631991</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.240982924045669</v>
+        <v>3.18669514893116</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.465587675321475</v>
+        <v>1.449990970538341</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.789480994459195</v>
+        <v>5.73986199542071</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.914691500833413</v>
+        <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.231861230090783</v>
+        <v>-4.266928227455542</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.221590584483352</v>
+        <v>3.167302809368843</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.45146576063401</v>
+        <v>1.435869055850876</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.78557095721382</v>
+        <v>5.735951958175334</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.964521442156941</v>
+        <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.179644920294441</v>
+        <v>-4.2147119176592</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.292307049725416</v>
+        <v>3.238019274610908</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.45146576063401</v>
+        <v>1.435869055850876</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.835400898537348</v>
+        <v>5.785781899498861</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.973335412366952</v>
+        <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.147747403209196</v>
+        <v>-4.182814400573954</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.313880026769525</v>
+        <v>3.259592251655016</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.483363277719256</v>
+        <v>1.467766572936122</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.863353378998506</v>
+        <v>5.81373437996002</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.849469723131095</v>
+        <v>3.7942621672848</v>
       </c>
       <c r="C2094" t="n">
-        <v>5.027002313160696</v>
+        <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.147747403209196</v>
+        <v>-4.16970887020147</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.313880026769525</v>
+        <v>3.260472047843207</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.483363277719256</v>
+        <v>1.467766572936122</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.020066110147064</v>
+        <v>5.809371963999217</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240921.xlsx
+++ b/tame_output/ON/bt/strategyON_20240921.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-578.5%</t>
+          <t>-578.6%</t>
         </is>
       </c>
     </row>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
@@ -49713,10 +49713,10 @@
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.16970887020147</v>
+        <v>-4.169810836049521</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.260472047843207</v>
+        <v>3.260431261503987</v>
       </c>
       <c r="F2094" t="n">
         <v>1.467766572936122</v>
